--- a/data/beverage_warmloop_260720.xlsx
+++ b/data/beverage_warmloop_260720.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sensory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipes" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instrumental" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dictionary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sensory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="recipes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="instrumental" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="dictionary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="process" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2784,11 +2785,6 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
@@ -2945,7 +2941,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -3168,7 +3163,6 @@
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1"/>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
@@ -3265,7 +3259,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
@@ -3325,4 +3318,138 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>왜 묻는가</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>프로파일</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>beverage_rice_milk</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>이 표가 어느 제형의 것인지</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>규모</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>주방 / 파일럿 / 공장</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>블록 이름</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RM-P1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>같은 공정끼리 묶는 이름. 공정을 바꾸면 새 이름을 주세요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>선언자</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>사용자</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>선언일</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>가열 — 가열 온도와 시간 (안 하면 '없음')</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>이 제형에서 바디감 에 걸립니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>공정 세부는 미상. '모두 같은 공정' 이라는 것만 확인됨 (2026-09-02 확인). 1 단계 목적은 동일성 판정이므로 세부가 비어 있어도 블록은 성립한다.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>그 밖에 남길 것</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>